--- a/Data/equipes_adverses.xlsx
+++ b/Data/equipes_adverses.xlsx
@@ -37,13 +37,13 @@
     <x:t>FootballAmericain</x:t>
   </x:si>
   <x:si>
-    <x:t>Les scorpion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Frederick-Bach</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/Image/ecole-de-lamitie/adverses/logos/19c12414-e00d-455f-a14d-b11449667e42.png</x:t>
+    <x:t>Scorpion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/Image/ecole-de-lamitie/adverses/logos/c0737839-0d80-48b0-b708-0f1a649a994a.avif</x:t>
   </x:si>
 </x:sst>
 </file>
